--- a/data/nse/delivery/daily_output/delivery_breakout_20260724.xlsx
+++ b/data/nse/delivery/daily_output/delivery_breakout_20260724.xlsx
@@ -504,10 +504,10 @@
         <v>56.3</v>
       </c>
       <c r="F2" t="n">
-        <v>1024318.4</v>
+        <v>1033661.448275862</v>
       </c>
       <c r="G2" t="n">
-        <v>87.08</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>3397.82</v>
@@ -534,10 +534,10 @@
         <v>17.44</v>
       </c>
       <c r="F3" t="n">
-        <v>330589.2333333333</v>
+        <v>324650.3448275862</v>
       </c>
       <c r="G3" t="n">
-        <v>7.56</v>
+        <v>7.7</v>
       </c>
       <c r="H3" t="n">
         <v>1249.4</v>
@@ -564,10 +564,10 @@
         <v>7.98</v>
       </c>
       <c r="F4" t="n">
-        <v>388514</v>
+        <v>393426.8275862069</v>
       </c>
       <c r="G4" t="n">
-        <v>5.35</v>
+        <v>5.28</v>
       </c>
       <c r="H4" t="n">
         <v>2011.24</v>
@@ -594,10 +594,10 @@
         <v>5.47</v>
       </c>
       <c r="F5" t="n">
-        <v>278522.1333333334</v>
+        <v>284988.724137931</v>
       </c>
       <c r="G5" t="n">
-        <v>15.45</v>
+        <v>15.1</v>
       </c>
       <c r="H5" t="n">
         <v>1519.11</v>
@@ -624,10 +624,10 @@
         <v>31.72</v>
       </c>
       <c r="F6" t="n">
-        <v>15638.23333333333</v>
+        <v>15782.93103448276</v>
       </c>
       <c r="G6" t="n">
-        <v>8.19</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>258.64</v>
@@ -654,10 +654,10 @@
         <v>7.87</v>
       </c>
       <c r="F7" t="n">
-        <v>177141.8333333333</v>
+        <v>178863.8275862069</v>
       </c>
       <c r="G7" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="H7" t="n">
         <v>686.04</v>
